--- a/Files/excel/certifications.xlsx
+++ b/Files/excel/certifications.xlsx
@@ -1,108 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Documents\Léandro\Travail\F-Career\MayGraphCards\MayGraphCards\MayGraphCards\Inputs backup\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2206FC5-7026-4319-AE4D-49EEADA7E851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AA470E5B-4010-458A-AD4F-F01BA0A1BAF3}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Serial Number</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Issued by</t>
-  </si>
-  <si>
-    <t>Jobs Related</t>
-  </si>
-  <si>
-    <t>Product Related</t>
-  </si>
-  <si>
-    <t>Microsoft Azure Fundamentals</t>
-  </si>
-  <si>
-    <t>Beginner</t>
-  </si>
-  <si>
-    <t>Microsoft Azure Fundamentals is an entry-level certification designed to introduce individuals to the core concepts and services of Microsoft Azure, focusing on cloud computing, Azure architecture, and basic management tools. It provides foundational knowledge for deploying, managing, and securing applications in the Azure cloud environment.</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>Cloud Administrator, Cloud Services Specialist</t>
-  </si>
-  <si>
-    <t>Azure</t>
-  </si>
-  <si>
-    <t>CER-000001</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
+      <name val="Calibri"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="128"/>
+      <family val="2"/>
       <sz val="6"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -124,45 +66,104 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="4" tint="0.59999389629810485"/>
+        <color theme="4" tint="0.5999938962981048"/>
       </left>
       <right style="thin">
-        <color theme="4" tint="0.59999389629810485"/>
+        <color theme="4" tint="0.5999938962981048"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.59999389629810485"/>
+        <color theme="4" tint="0.5999938962981048"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.59999389629810485"/>
+        <color theme="4" tint="0.5999938962981048"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -462,66 +463,97 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C96BB0-F64F-4863-82FB-F0C667585417}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="17.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.36328125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="31.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="33.6328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="13" style="1"/>
+    <col width="17.08984375" customWidth="1" style="1" min="1" max="2"/>
+    <col width="32.36328125" customWidth="1" style="1" min="3" max="3"/>
+    <col width="31.7265625" customWidth="1" style="1" min="4" max="5"/>
+    <col width="33.6328125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="19.54296875" customWidth="1" style="1" min="7" max="7"/>
+    <col width="13" customWidth="1" style="1" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>issued_by</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>products</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>serial_number</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Fundamentals</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Fundamentals is an entry-level certification designed to introduce individuals to the core concepts and services of Microsoft Azure, focusing on cloud computing, Azure architecture, and basic management tools. It provides foundational knowledge for deploying, managing, and securing applications in the Azure cloud environment.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cloud Administrator, Cloud Services Specialist</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CER-000001</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Files/excel/certifications.xlsx
+++ b/Files/excel/certifications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Documents\Léandro\Travail\F-Career\MayGraphCards\MayGraphCards\MayGraphCards\Inputs backup\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/Files/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2206FC5-7026-4319-AE4D-49EEADA7E851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1114895B-A4CE-444F-9976-061D23879D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AA470E5B-4010-458A-AD4F-F01BA0A1BAF3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="10300" xr2:uid="{AA470E5B-4010-458A-AD4F-F01BA0A1BAF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,29 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Serial Number</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Issued by</t>
-  </si>
-  <si>
-    <t>Jobs Related</t>
-  </si>
-  <si>
-    <t>Product Related</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Microsoft Azure Fundamentals</t>
   </si>
@@ -68,13 +46,40 @@
   </si>
   <si>
     <t>CER-000001</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>issuedBy</t>
+  </si>
+  <si>
+    <t>products</t>
+  </si>
+  <si>
+    <t>jobs</t>
+  </si>
+  <si>
+    <t>serialNumber</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>updated_at</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,7 +119,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -137,18 +142,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.59999389629810485"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.59999389629810485"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -167,9 +184,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -207,7 +224,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -313,7 +330,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -455,7 +472,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -463,61 +480,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C96BB0-F64F-4863-82FB-F0C667585417}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="14.5"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="17.08984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.36328125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="31.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="33.6328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="17.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="31.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5" style="1" customWidth="1"/>
     <col min="8" max="16384" width="13" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
